--- a/data/trans_dic/P15A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,6</t>
+          <t>1,61; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,95</t>
+          <t>1,62; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,02</t>
+          <t>1,81; 4,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,77</t>
+          <t>1,6; 3,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,54</t>
+          <t>2,6; 4,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,37</t>
+          <t>2,39; 4,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,83</t>
+          <t>3,03; 5,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,55</t>
+          <t>4,17; 6,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,81</t>
+          <t>2,38; 3,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,63</t>
+          <t>2,18; 3,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,62</t>
+          <t>2,75; 4,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,98</t>
+          <t>3,34; 4,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,63</t>
+          <t>3,74; 5,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,07</t>
+          <t>2,37; 4,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,39</t>
+          <t>1,97; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,01</t>
+          <t>1,31; 2,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,03</t>
+          <t>1,51; 2,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,06</t>
+          <t>1,65; 3,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,23</t>
+          <t>1,09; 2,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,52</t>
+          <t>1,24; 2,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,18</t>
+          <t>2,85; 4,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,26</t>
+          <t>2,24; 3,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,62</t>
+          <t>1,7; 2,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,53</t>
+          <t>1,51; 2,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,54</t>
+          <t>2,08; 5,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,82</t>
+          <t>1,51; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,91</t>
+          <t>1,06; 3,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,4</t>
+          <t>0,75; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,65</t>
+          <t>1,48; 4,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,0</t>
+          <t>1,75; 5,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,06</t>
+          <t>1,38; 4,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,54</t>
+          <t>1,02; 2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,59</t>
+          <t>2,13; 4,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,49</t>
+          <t>2,02; 4,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,53</t>
+          <t>1,49; 3,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,55</t>
+          <t>1,05; 2,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,42</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,58</t>
+          <t>2,34; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,17</t>
+          <t>2,06; 3,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,66</t>
+          <t>1,54; 2,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,4</t>
+          <t>2,23; 3,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,34</t>
+          <t>2,2; 3,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,12</t>
+          <t>1,99; 3,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,09</t>
+          <t>1,97; 3,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,77</t>
+          <t>2,87; 3,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,25</t>
+          <t>2,45; 3,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,98</t>
+          <t>2,18; 2,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,71</t>
+          <t>1,91; 2,68</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17176; 37117</t>
+          <t>16638; 36396</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15411; 38484</t>
+          <t>15819; 37566</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13577; 30349</t>
+          <t>13625; 30586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8457; 19436</t>
+          <t>8214; 19687</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33328; 59703</t>
+          <t>34224; 60424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32345; 58419</t>
+          <t>32008; 58691</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30438; 58032</t>
+          <t>30168; 57557</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31234; 49502</t>
+          <t>31515; 48274</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55385; 89332</t>
+          <t>55786; 89490</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51931; 83826</t>
+          <t>50380; 85549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47617; 80892</t>
+          <t>48016; 79822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42094; 63302</t>
+          <t>42447; 62784</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60459; 95378</t>
+          <t>63335; 98133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47665; 80009</t>
+          <t>46542; 78526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40429; 70401</t>
+          <t>40813; 70120</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31006; 68982</t>
+          <t>29981; 67462</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24505; 48052</t>
+          <t>24017; 46732</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28213; 53726</t>
+          <t>28997; 54495</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20764; 44262</t>
+          <t>21637; 46009</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27608; 56364</t>
+          <t>27675; 56148</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93964; 137299</t>
+          <t>93622; 138015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81652; 121390</t>
+          <t>83189; 124057</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67662; 106594</t>
+          <t>68915; 106754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67233; 114396</t>
+          <t>68478; 114393</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11551; 30549</t>
+          <t>11469; 31383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6945; 23203</t>
+          <t>7281; 23570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6057; 21388</t>
+          <t>5820; 21075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4808; 21982</t>
+          <t>4859; 22555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6366; 22156</t>
+          <t>7061; 21631</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8436; 27535</t>
+          <t>8035; 25974</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7329; 22278</t>
+          <t>7566; 23267</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6434; 16801</t>
+          <t>6716; 16972</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22442; 47136</t>
+          <t>21862; 46379</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18548; 42206</t>
+          <t>18950; 42676</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17178; 38647</t>
+          <t>16374; 37320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13922; 33299</t>
+          <t>13769; 33301</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>102111; 144855</t>
+          <t>103130; 147090</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79204; 122541</t>
+          <t>79933; 119072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70392; 107003</t>
+          <t>69741; 106532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52434; 91869</t>
+          <t>53315; 94183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75288; 115059</t>
+          <t>75267; 116065</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79374; 118674</t>
+          <t>78075; 120934</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68628; 110214</t>
+          <t>70194; 110290</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72830; 112957</t>
+          <t>71932; 110327</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>189848; 251213</t>
+          <t>190759; 249424</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>169874; 226958</t>
+          <t>171054; 229339</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149330; 206168</t>
+          <t>150882; 203058</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>136761; 192298</t>
+          <t>135995; 190764</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,53</t>
+          <t>1,59; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,85</t>
+          <t>1,55; 3,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,05</t>
+          <t>1,86; 4,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,82</t>
+          <t>1,43; 3,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,59</t>
+          <t>2,54; 4,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,39</t>
+          <t>2,44; 4,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,79</t>
+          <t>3,12; 5,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,39</t>
+          <t>3,96; 6,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,81</t>
+          <t>2,39; 3,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,7</t>
+          <t>2,26; 3,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,56</t>
+          <t>2,83; 4,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,94</t>
+          <t>3,15; 4,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,79</t>
+          <t>3,69; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,0</t>
+          <t>2,42; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,38</t>
+          <t>1,92; 3,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,95</t>
+          <t>1,82; 3,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,94</t>
+          <t>1,57; 3,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,1</t>
+          <t>1,61; 3,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,31</t>
+          <t>1,07; 2,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,51</t>
+          <t>1,54; 2,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,21</t>
+          <t>2,9; 4,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,33</t>
+          <t>2,24; 3,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,63</t>
+          <t>1,67; 2,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,53</t>
+          <t>1,79; 2,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,69</t>
+          <t>2,02; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,9</t>
+          <t>1,41; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,85</t>
+          <t>1,23; 3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,49</t>
+          <t>0,82; 3,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,54</t>
+          <t>1,42; 4,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,66</t>
+          <t>1,63; 5,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,24</t>
+          <t>1,42; 3,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,57</t>
+          <t>1,13; 2,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,51</t>
+          <t>2,23; 4,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,54</t>
+          <t>1,96; 4,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,41</t>
+          <t>1,51; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,55</t>
+          <t>1,18; 2,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,14; 4,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,48</t>
+          <t>2,33; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,15</t>
+          <t>2,09; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,73</t>
+          <t>1,78; 2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,43</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,4</t>
+          <t>2,22; 3,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,12</t>
+          <t>1,95; 3,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,02</t>
+          <t>2,17; 3,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,75</t>
+          <t>2,86; 3,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,29</t>
+          <t>2,45; 3,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,94</t>
+          <t>2,18; 2,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 2,68</t>
+          <t>2,12; 2,85</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>40749</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>54280</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16638; 36396</t>
+          <t>16444; 36145</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15819; 37566</t>
+          <t>15139; 36818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13625; 30586</t>
+          <t>14058; 31165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8214; 19687</t>
+          <t>8298; 20935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34224; 60424</t>
+          <t>33402; 61304</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32008; 58691</t>
+          <t>32585; 56950</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30168; 57557</t>
+          <t>31058; 58265</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31515; 48274</t>
+          <t>32571; 51397</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55786; 89490</t>
+          <t>56016; 89615</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50380; 85549</t>
+          <t>52294; 84897</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48016; 79822</t>
+          <t>49552; 80817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42447; 62784</t>
+          <t>44094; 65590</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>55442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89226</t>
+          <t>99880</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63335; 98133</t>
+          <t>62559; 97144</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46542; 78526</t>
+          <t>47469; 78998</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40813; 70120</t>
+          <t>39970; 69416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29981; 67462</t>
+          <t>40612; 77390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24017; 46732</t>
+          <t>24946; 49420</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28997; 54495</t>
+          <t>28315; 53756</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21637; 46009</t>
+          <t>21369; 45627</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27675; 56148</t>
+          <t>33476; 60633</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93622; 138015</t>
+          <t>94995; 135456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83189; 124057</t>
+          <t>83380; 125283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68915; 106754</t>
+          <t>67788; 104757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68478; 114393</t>
+          <t>78857; 124376</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>25659</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11469; 31383</t>
+          <t>11131; 29909</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7281; 23570</t>
+          <t>6776; 23563</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5820; 21075</t>
+          <t>6729; 20991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4859; 22555</t>
+          <t>5808; 22145</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7061; 21631</t>
+          <t>6775; 22706</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8035; 25974</t>
+          <t>7488; 25577</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7566; 23267</t>
+          <t>7809; 21684</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6716; 16972</t>
+          <t>8336; 20554</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21862; 46379</t>
+          <t>22886; 47152</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18950; 42676</t>
+          <t>18446; 41932</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16374; 37320</t>
+          <t>16550; 37725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13769; 33301</t>
+          <t>17001; 38041</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71746</t>
+          <t>81049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90896</t>
+          <t>98770</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>162642</t>
+          <t>179819</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103130; 147090</t>
+          <t>102848; 146963</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79933; 119072</t>
+          <t>79532; 119027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69741; 106532</t>
+          <t>70714; 106822</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53315; 94183</t>
+          <t>62766; 104852</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75267; 116065</t>
+          <t>75895; 113942</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78075; 120934</t>
+          <t>78935; 122308</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70194; 110290</t>
+          <t>68820; 107479</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71932; 110327</t>
+          <t>81048; 118244</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190759; 249424</t>
+          <t>190398; 247827</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>171054; 229339</t>
+          <t>171094; 227506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>150882; 203058</t>
+          <t>150717; 204200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>135995; 190764</t>
+          <t>154016; 206914</t>
         </is>
       </c>
     </row>
